--- a/Outfeed_Test.xlsx
+++ b/Outfeed_Test.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gatmichar\Documents\eiddpython\eidppython24w-code\lecture_01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gatmichar\Documents\fruit_salad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A4FECD-A02B-43E1-A074-399FC053741E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED7DC52-F335-4C29-8AE2-6C6C78757DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="3495" windowWidth="21600" windowHeight="11295" xr2:uid="{674A2589-6D5B-4C35-BFDA-084D70AE4967}"/>
+    <workbookView xWindow="2760" yWindow="-15300" windowWidth="21600" windowHeight="11295" xr2:uid="{674A2589-6D5B-4C35-BFDA-084D70AE4967}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -38,18 +38,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
-    <t>OUT-ID</t>
-  </si>
-  <si>
     <t>article_code</t>
   </si>
   <si>
     <t>article_description</t>
   </si>
   <si>
-    <t>OUT-quantity</t>
-  </si>
-  <si>
     <t>shop_destination</t>
   </si>
   <si>
@@ -78,6 +72,12 @@
   </si>
   <si>
     <t>FINOCCHI</t>
+  </si>
+  <si>
+    <t>OUT_ID</t>
+  </si>
+  <si>
+    <t>OUT_quantity</t>
   </si>
 </sst>
 </file>
@@ -458,19 +458,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -478,13 +478,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>20</v>
@@ -495,13 +495,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>40</v>
@@ -512,13 +512,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>40</v>
@@ -529,13 +529,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>10</v>

--- a/Outfeed_Test.xlsx
+++ b/Outfeed_Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gatmichar\Documents\fruit_salad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED7DC52-F335-4C29-8AE2-6C6C78757DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFE1FB6-E36D-4A49-A10C-516BE8730639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="-15300" windowWidth="21600" windowHeight="11295" xr2:uid="{674A2589-6D5B-4C35-BFDA-084D70AE4967}"/>
+    <workbookView xWindow="14310" yWindow="-21600" windowWidth="19410" windowHeight="20985" xr2:uid="{674A2589-6D5B-4C35-BFDA-084D70AE4967}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>article_code</t>
   </si>
@@ -50,12 +50,6 @@
     <t>WAS</t>
   </si>
   <si>
-    <t>AFF</t>
-  </si>
-  <si>
-    <t>PIO</t>
-  </si>
-  <si>
     <t>753122</t>
   </si>
   <si>
@@ -66,12 +60,6 @@
   </si>
   <si>
     <t>CAROTE NAT RESIDUO ZERO</t>
-  </si>
-  <si>
-    <t>763345</t>
-  </si>
-  <si>
-    <t>FINOCCHI</t>
   </si>
   <si>
     <t>OUT_ID</t>
@@ -449,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DF75E4-4F0B-4D4B-AAD6-82387B27C378}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="25.28515625" bestFit="1" customWidth="1"/>
@@ -458,7 +446,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -470,7 +458,7 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -478,10 +466,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -495,50 +483,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
       <c r="E3">
         <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Outfeed_Test.xlsx
+++ b/Outfeed_Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gatmichar\Documents\fruit_salad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFE1FB6-E36D-4A49-A10C-516BE8730639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35156C3-9C08-453A-9A9B-5EBC505DFBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14310" yWindow="-21600" windowWidth="19410" windowHeight="20985" xr2:uid="{674A2589-6D5B-4C35-BFDA-084D70AE4967}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>article_code</t>
   </si>
@@ -50,6 +50,12 @@
     <t>WAS</t>
   </si>
   <si>
+    <t>AFF</t>
+  </si>
+  <si>
+    <t>PIO</t>
+  </si>
+  <si>
     <t>753122</t>
   </si>
   <si>
@@ -60,6 +66,12 @@
   </si>
   <si>
     <t>CAROTE NAT RESIDUO ZERO</t>
+  </si>
+  <si>
+    <t>763345</t>
+  </si>
+  <si>
+    <t>FINOCCHI</t>
   </si>
   <si>
     <t>OUT_ID</t>
@@ -437,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DF75E4-4F0B-4D4B-AAD6-82387B27C378}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="25.28515625" bestFit="1" customWidth="1"/>
@@ -446,7 +458,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -458,7 +470,7 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -466,16 +478,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -483,16 +495,50 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
       <c r="E3">
         <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Outfeed_Test.xlsx
+++ b/Outfeed_Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gatmichar\Documents\fruit_salad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35156C3-9C08-453A-9A9B-5EBC505DFBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67A893A-F379-4077-8577-F3EAC561EE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14310" yWindow="-21600" windowWidth="19410" windowHeight="20985" xr2:uid="{674A2589-6D5B-4C35-BFDA-084D70AE4967}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
   <si>
     <t>article_code</t>
   </si>
@@ -68,16 +68,16 @@
     <t>CAROTE NAT RESIDUO ZERO</t>
   </si>
   <si>
-    <t>763345</t>
-  </si>
-  <si>
-    <t>FINOCCHI</t>
-  </si>
-  <si>
     <t>OUT_ID</t>
   </si>
   <si>
     <t>OUT_quantity</t>
+  </si>
+  <si>
+    <t>753055</t>
+  </si>
+  <si>
+    <t>CAVOLFIORE BIO</t>
   </si>
 </sst>
 </file>
@@ -113,8 +113,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -449,16 +450,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DF75E4-4F0B-4D4B-AAD6-82387B27C378}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -470,10 +471,10 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -484,13 +485,13 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -501,45 +502,207 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5">
         <v>5</v>
       </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
